--- a/Employee_Reports_wi48/James Kariungi Muthee Q0525.xlsx
+++ b/Employee_Reports_wi48/James Kariungi Muthee Q0525.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-335</v>
+        <v>-338</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -998,11 +998,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1070,9 +1070,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>11-Jun-2026</t>
@@ -1084,11 +1096,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1121,11 +1133,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1170,11 +1182,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1219,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
